--- a/data/000957_中通客车_财务数据.xlsx
+++ b/data/000957_中通客车_财务数据.xlsx
@@ -10715,7 +10715,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -17057,7 +17057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -17087,8 +17087,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17135,22 +17133,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -17160,75 +17158,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -17262,58 +17250,52 @@
         <v>3.234997914704034</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>0.7010560719402823</v>
+      <c r="J2" s="3" t="n">
+        <v>68.01534273694631</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>68.01534273694631</v>
+        <v>1.321376736471076</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1.321376736471076</v>
+        <v>1.267675720505909</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1.267675720505909</v>
+        <v>212.6499032882012</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>2.293086508067872</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>156.9936409871129</v>
+        <v>32.44145659633205</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>32.44145659633205</v>
+        <v>1.14540834361173</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>11.09691233903175</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>1.14540834361173</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>1.45256397820022</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="V2" s="6" t="n">
+        <v>-0.028250099748817</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>-103644800</v>
+      </c>
       <c r="X2" s="6" t="n">
-        <v>-0.028250099748817</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>-103644800</v>
-      </c>
-      <c r="Z2" s="6" t="n">
         <v>0.9004892186638687</v>
       </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>−/−/−</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>2.224745276679535</v>
+      </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>−/−/−</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>2.224745276679535</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -17350,63 +17332,57 @@
         <v>1.871880569895847</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>1.597332451779215</v>
+        <v>77.58731691614356</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>77.58731691614356</v>
+        <v>1.302734375</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.302734375</v>
+        <v>1.253173828125</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.253173828125</v>
+        <v>346.1759425493717</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>1.360287450627166</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>264.6499457405276</v>
-      </c>
-      <c r="P3" s="3" t="n">
         <v>23.1324325677594</v>
       </c>
-      <c r="Q3" s="3" t="n">
-        <v>15.56256562925191</v>
-      </c>
-      <c r="R3" s="6" t="n">
+      <c r="P3" s="6" t="n">
         <v>0.7657089101833431</v>
       </c>
-      <c r="S3" s="6" t="n">
+      <c r="Q3" s="6" t="n">
         <v>0.9212765227362864</v>
       </c>
-      <c r="T3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="3" t="n">
+        <v>-15.18399247137272</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>-67.35039606234469</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>-15.18399247137272</v>
+        <v>53.74907201187826</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>-67.35039606234469</v>
+        <v>-4.870158724259472</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>53.74907201187826</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>-4.870158724259472</v>
-      </c>
-      <c r="Y3" s="3" t="n">
         <v>-1048000000</v>
       </c>
-      <c r="Z3" s="6" t="n">
+      <c r="X3" s="6" t="n">
         <v>0.4771014749095328</v>
       </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>1.322290209537697</v>
+      </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>1.322290209537697</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -17443,63 +17419,57 @@
         <v>3.290782086055625</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2.577450809148885</v>
+        <v>77.86396668571895</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>77.86396668571895</v>
+        <v>1.377679038159958</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.377679038159958</v>
+        <v>1.310637741766858</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.310637741766858</v>
+        <v>351.7521209885651</v>
       </c>
       <c r="N4" s="6" t="n">
         <v>0.8305220099603771</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>433.4623233129909</v>
-      </c>
-      <c r="P4" s="3" t="n">
         <v>12.99669538130577</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>27.69934890663192</v>
-      </c>
-      <c r="R4" s="6" t="n">
+      <c r="P4" s="6" t="n">
         <v>0.4927321842418838</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="Q4" s="6" t="n">
         <v>0.5730734977750541</v>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="3" t="n">
+        <v>-22.58129908463433</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-80.86919162770432</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>-22.58129908463433</v>
+        <v>-1.440527925317882</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>-80.86919162770432</v>
+        <v>-20.42587712076919</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>-1.440527925317882</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>-20.42587712076919</v>
-      </c>
-      <c r="Y4" s="3" t="n">
         <v>-791065800</v>
       </c>
-      <c r="Z4" s="6" t="n">
+      <c r="X4" s="6" t="n">
         <v>0.730596991784318</v>
       </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>1.195903672222622</v>
+      </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>1.195903672222622</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -17536,63 +17506,57 @@
         <v>3.740322485196045</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.17476447207022</v>
+        <v>77.31565865782933</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>77.31565865782933</v>
+        <v>1.272429435483871</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.272429435483871</v>
+        <v>1.201864919354839</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.201864919354839</v>
+        <v>340.7082876962395</v>
       </c>
       <c r="N5" s="6" t="n">
         <v>0.9827657073256068</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>366.3131480031649</v>
-      </c>
-      <c r="P5" s="3" t="n">
         <v>12.30049676313141</v>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>29.26711066491535</v>
-      </c>
-      <c r="R5" s="6" t="n">
+      <c r="P5" s="6" t="n">
         <v>0.5544500858987539</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="Q5" s="6" t="n">
         <v>0.6532249388953488</v>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="3" t="n">
+        <v>10.90204659435505</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>-9.56871522806825</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>10.90204659435505</v>
+        <v>-1.445251898424104</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-9.56871522806825</v>
+        <v>31.29549044268091</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-1.445251898424104</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>31.29549044268091</v>
-      </c>
-      <c r="Y5" s="3" t="n">
         <v>730000000</v>
       </c>
-      <c r="Z5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>0.8848466149293674</v>
       </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>1.181371734584025</v>
+      </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>1.181371734584025</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -17629,63 +17593,57 @@
         <v>5.214129463799006</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2.925851130046982</v>
+        <v>73.57428952889568</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>73.57428952889568</v>
+        <v>1.36676670352235</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1.36676670352235</v>
+        <v>1.274522192386669</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.274522192386669</v>
+        <v>278.3189033189033</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>0.8639804585945311</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>416.6760907829157</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>8.070311006206294</v>
       </c>
-      <c r="Q6" s="3" t="n">
-        <v>44.60794630134451</v>
-      </c>
-      <c r="R6" s="6" t="n">
+      <c r="P6" s="6" t="n">
         <v>0.3908136468806526</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>0.4701185333603541</v>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="3" t="n">
+        <v>-34.61782607788861</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-28.87101325617136</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>-34.61782607788861</v>
+        <v>-13.12344656172328</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-28.87101325617136</v>
+        <v>12.37051496633936</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-13.12344656172328</v>
+        <v>246949400</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>12.37051496633936</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>246949400</v>
+        <v>1.180008248206924</v>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.180008248206924</v>
+        <v>1.166395639296217</v>
       </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>1.166395639296217</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -17722,63 +17680,57 @@
         <v>5.124473153609332</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.7598368942989</v>
+        <v>74.08607594936709</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>74.08607594936709</v>
+        <v>1.162461717952457</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.162461717952457</v>
+        <v>1.096835350736474</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.096835350736474</v>
+        <v>285.8929269245799</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>1.315541088705005</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>273.6516579306371</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>9.431815164564798</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>38.16868690901781</v>
-      </c>
-      <c r="R7" s="6" t="n">
+      <c r="P7" s="6" t="n">
         <v>0.4505313104238496</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="Q7" s="6" t="n">
         <v>0.5518087109925409</v>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="3" t="n">
+        <v>4.06202573187783</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-1033.227794603726</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>4.06202573187783</v>
+        <v>-5.826816707991608</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>-1033.227794603726</v>
+        <v>-4.149784096647837</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>-5.826816707991608</v>
+        <v>850892100</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>-4.149784096647837</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>850892100</v>
-      </c>
-      <c r="Z7" s="3" t="n">
         <v>1.004440291988499</v>
       </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
+      </c>
+      <c r="Z7" s="6" t="n">
+        <v>0.9366896410249916</v>
+      </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB7" s="6" t="n">
-        <v>0.9366896410249916</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -17814,64 +17766,58 @@
       <c r="I8" s="3" t="n">
         <v>3.516765645712154</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>-0.1033287019429749</v>
+      <c r="J8" s="3" t="n">
+        <v>71.5734415029889</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>71.5734415029889</v>
+        <v>1.186562400255346</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.186562400255346</v>
+        <v>1.113629109479732</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.113629109479732</v>
+        <v>251.7837025910627</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>1.412254522853319</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>254.9115574950725</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>11.32019608972437</v>
       </c>
-      <c r="Q8" s="3" t="n">
-        <v>31.8015692614001</v>
-      </c>
-      <c r="R8" s="6" t="n">
+      <c r="P8" s="6" t="n">
         <v>0.5483742553011485</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="Q8" s="6" t="n">
         <v>0.6849516938050111</v>
       </c>
-      <c r="T8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="3" t="n">
+        <v>15.03387649292586</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>144.7896304894714</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>15.03387649292586</v>
+        <v>-5.134177215189874</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>144.7896304894714</v>
+        <v>11.88896795880888</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>-5.134177215189874</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>11.88896795880888</v>
-      </c>
-      <c r="Y8" s="3" t="n">
         <v>1151716400</v>
       </c>
-      <c r="Z8" s="6" t="n">
+      <c r="X8" s="6" t="n">
         <v>0.8978081488327968</v>
       </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>1.245180771715901</v>
+      </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>1.245180771715901</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -17907,64 +17853,58 @@
       <c r="I9" s="3" t="n">
         <v>5.15408018448388</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>-0.2094965888450837</v>
+      <c r="J9" s="3" t="n">
+        <v>67.92852104396896</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>67.92852104396896</v>
+        <v>1.243151969981239</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1.243151969981239</v>
+        <v>1.123452157598499</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1.123452157598499</v>
+        <v>211.7259069256138</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>1.125691315625995</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>319.8034798729923</v>
-      </c>
-      <c r="P9" s="3" t="n">
         <v>7.296081095159817</v>
       </c>
-      <c r="Q9" s="3" t="n">
-        <v>49.34155683094342</v>
-      </c>
-      <c r="R9" s="6" t="n">
+      <c r="P9" s="6" t="n">
         <v>0.4748636298433478</v>
       </c>
-      <c r="S9" s="6" t="n">
+      <c r="Q9" s="6" t="n">
         <v>0.6036350558153758</v>
       </c>
-      <c r="T9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="3" t="n">
+        <v>-19.56578567400732</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>-29.16040939383927</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>-19.56578567400732</v>
+        <v>-9.201537147736977</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>-29.16040939383927</v>
+        <v>6.25950646123363</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>-9.201537147736977</v>
+        <v>434700900.0000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>6.25950646123363</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>434700900.0000001</v>
+        <v>1.148483761347601</v>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1.148483761347601</v>
+        <v>1.281467737800078</v>
       </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>1.281467737800078</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18000,64 +17940,58 @@
       <c r="I10" s="3" t="n">
         <v>4.115715685441479</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>-0.5596802341789987</v>
+      <c r="J10" s="3" t="n">
+        <v>63.95249173503122</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>63.95249173503122</v>
+        <v>1.346555323590814</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.346555323590814</v>
+        <v>1.179958246346555</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.179958246346555</v>
+        <v>177.4116847826087</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>1.965340419917738</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>183.174373432501</v>
-      </c>
-      <c r="P10" s="3" t="n">
         <v>7.45878542149025</v>
       </c>
-      <c r="Q10" s="3" t="n">
-        <v>48.2652308193192</v>
-      </c>
-      <c r="R10" s="6" t="n">
+      <c r="P10" s="6" t="n">
         <v>0.6878043153733581</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="Q10" s="6" t="n">
         <v>0.8770083626659528</v>
       </c>
-      <c r="T10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="3" t="n">
+        <v>35.11015274658711</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>258.1221725282604</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>35.11015274658711</v>
+        <v>-3.985422055019986</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>258.1221725282604</v>
+        <v>5.736698507301984</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>-3.985422055019986</v>
+        <v>1430817600</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>5.736698507301984</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>1430817600</v>
+        <v>1.209826362469065</v>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>1.209826362469065</v>
+        <v>1.707073019367625</v>
       </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>1.707073019367625</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18093,64 +18027,58 @@
       <c r="I11" s="3" t="n">
         <v>3.479108397542044</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>-0.1503265506730528</v>
+      <c r="J11" s="3" t="n">
+        <v>68.19884580338159</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>68.19884580338159</v>
+        <v>1.242200328407225</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.242200328407225</v>
+        <v>1.073727422003284</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.073727422003284</v>
+        <v>214.4539955428208</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>2.773006383836549</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>129.8229971984153</v>
-      </c>
-      <c r="P11" s="3" t="n">
         <v>7.454908201513158</v>
       </c>
+      <c r="P11" s="6" t="n">
+        <v>0.8123537876834405</v>
+      </c>
       <c r="Q11" s="3" t="n">
-        <v>48.29033306230775</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0.8123537876834405</v>
-      </c>
+        <v>1.045887388152694</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>1.045887388152694</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
+        <v>27.82016731346433</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>44.17944857751748</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>27.82016731346433</v>
+        <v>20.93792090118771</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>44.17944857751748</v>
+        <v>3.130815120760734</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>20.93792090118771</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>3.130815120760734</v>
-      </c>
-      <c r="Y11" s="3" t="n">
         <v>1118801500</v>
       </c>
-      <c r="Z11" s="6" t="n">
+      <c r="X11" s="6" t="n">
         <v>0.9986279443553217</v>
       </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>1.636288065074305</v>
+      </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>1.636288065074305</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
